--- a/static/excel_files/NA_ADT_FTV.xlsx
+++ b/static/excel_files/NA_ADT_FTV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jesusalberca/Desktop/qc_matrix_generator/static/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0E008A-91BD-1A47-800E-C6A955B22890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511A1B0C-5588-A644-B91A-4EF8234D857F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20580" yWindow="640" windowWidth="30440" windowHeight="20780" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -493,7 +493,55 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF783F04"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF9CB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FF0000FF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF660000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEA9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF7F6000"/>
@@ -806,8 +854,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="14.33203125" customWidth="1"/>
-    <col min="3" max="5" width="19.6640625" customWidth="1"/>
-    <col min="6" max="6" width="78.6640625" customWidth="1"/>
+    <col min="3" max="4" width="19.6640625" customWidth="1"/>
+    <col min="5" max="5" width="78.83203125" customWidth="1"/>
+    <col min="6" max="6" width="30.83203125" customWidth="1"/>
     <col min="7" max="8" width="19.5" customWidth="1"/>
     <col min="9" max="9" width="16.33203125" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
@@ -853,6 +902,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="32" customHeight="1">
+      <c r="A2" s="3"/>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -860,22 +910,23 @@
         <v>4</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="3"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
     </row>
     <row r="3" spans="1:12" ht="32" customHeight="1">
+      <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
@@ -883,22 +934,23 @@
         <v>4</v>
       </c>
       <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="F3" s="5"/>
       <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="5"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12" ht="32" customHeight="1">
+      <c r="A4" s="3"/>
       <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
@@ -906,22 +958,23 @@
         <v>4</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:12" ht="32" customHeight="1">
+      <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
         <v>3</v>
       </c>
@@ -929,22 +982,23 @@
         <v>4</v>
       </c>
       <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>12</v>
       </c>
+      <c r="F5" s="5"/>
       <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
     </row>
     <row r="6" spans="1:12" ht="32" customHeight="1">
+      <c r="A6" s="3"/>
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
@@ -952,22 +1006,23 @@
         <v>4</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="3"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
     <row r="7" spans="1:12" ht="32" customHeight="1">
+      <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
         <v>10</v>
       </c>
@@ -975,22 +1030,23 @@
         <v>4</v>
       </c>
       <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>14</v>
       </c>
+      <c r="F7" s="5"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="5"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:12" ht="32" customHeight="1">
+      <c r="A8" s="3"/>
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -998,22 +1054,23 @@
         <v>4</v>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" s="3"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
     </row>
     <row r="9" spans="1:12" ht="32" customHeight="1">
+      <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
         <v>10</v>
       </c>
@@ -1021,22 +1078,23 @@
         <v>4</v>
       </c>
       <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="F9" s="5"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="6" t="s">
+      <c r="H9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="5"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="1:12" ht="32" customHeight="1">
+      <c r="A10" s="3"/>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1044,22 +1102,23 @@
         <v>18</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="3"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
     </row>
     <row r="11" spans="1:12" ht="32" customHeight="1">
+      <c r="A11" s="5"/>
       <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
@@ -1067,22 +1126,23 @@
         <v>18</v>
       </c>
       <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>20</v>
       </c>
+      <c r="F11" s="5"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J11" s="5"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:12" ht="32" customHeight="1">
+      <c r="A12" s="3"/>
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1090,22 +1150,23 @@
         <v>18</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" s="3"/>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
     </row>
     <row r="13" spans="1:12" ht="32" customHeight="1">
+      <c r="A13" s="5"/>
       <c r="B13" s="6" t="s">
         <v>10</v>
       </c>
@@ -1113,22 +1174,23 @@
         <v>18</v>
       </c>
       <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>22</v>
       </c>
+      <c r="F13" s="5"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="6" t="s">
+      <c r="H13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" s="5"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="1:12" ht="32" customHeight="1">
+      <c r="A14" s="3"/>
       <c r="B14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1136,22 +1198,23 @@
         <v>18</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J14" s="3"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
     <row r="15" spans="1:12" ht="32" customHeight="1">
+      <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
         <v>10</v>
       </c>
@@ -1159,22 +1222,23 @@
         <v>18</v>
       </c>
       <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>24</v>
       </c>
+      <c r="F15" s="5"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="6" t="s">
+      <c r="H15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J15" s="5"/>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
     </row>
     <row r="16" spans="1:12" ht="32" customHeight="1">
+      <c r="A16" s="3"/>
       <c r="B16" s="1" t="s">
         <v>10</v>
       </c>
@@ -1182,22 +1246,23 @@
         <v>18</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J16" s="3"/>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
     </row>
-    <row r="17" spans="2:12" ht="32" customHeight="1">
+    <row r="17" spans="1:12" ht="32" customHeight="1">
+      <c r="A17" s="5"/>
       <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
@@ -1205,22 +1270,23 @@
         <v>18</v>
       </c>
       <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>26</v>
       </c>
+      <c r="F17" s="5"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="6" t="s">
+      <c r="H17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J17" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J17" s="5"/>
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
     </row>
-    <row r="18" spans="2:12" ht="32" customHeight="1">
+    <row r="18" spans="1:12" ht="32" customHeight="1">
+      <c r="A18" s="3"/>
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
@@ -1228,22 +1294,23 @@
         <v>18</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J18" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J18" s="3"/>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
     </row>
-    <row r="19" spans="2:12" ht="32" customHeight="1">
+    <row r="19" spans="1:12" ht="32" customHeight="1">
+      <c r="A19" s="5"/>
       <c r="B19" s="6" t="s">
         <v>10</v>
       </c>
@@ -1251,22 +1318,23 @@
         <v>18</v>
       </c>
       <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="F19" s="5"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="6" t="s">
+      <c r="H19" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J19" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J19" s="5"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
     </row>
-    <row r="20" spans="2:12" ht="32" customHeight="1">
+    <row r="20" spans="1:12" ht="32" customHeight="1">
+      <c r="A20" s="3"/>
       <c r="B20" s="1" t="s">
         <v>10</v>
       </c>
@@ -1274,22 +1342,23 @@
         <v>18</v>
       </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J20" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J20" s="3"/>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
     </row>
-    <row r="21" spans="2:12" ht="32" customHeight="1">
+    <row r="21" spans="1:12" ht="32" customHeight="1">
+      <c r="A21" s="5"/>
       <c r="B21" s="6" t="s">
         <v>10</v>
       </c>
@@ -1297,22 +1366,23 @@
         <v>18</v>
       </c>
       <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>29</v>
       </c>
+      <c r="F21" s="5"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J21" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
     </row>
-    <row r="22" spans="2:12" ht="32" customHeight="1">
+    <row r="22" spans="1:12" ht="32" customHeight="1">
+      <c r="A22" s="3"/>
       <c r="B22" s="1" t="s">
         <v>10</v>
       </c>
@@ -1320,22 +1390,23 @@
         <v>18</v>
       </c>
       <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J22" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J22" s="3"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
     </row>
-    <row r="23" spans="2:12" ht="32" customHeight="1">
+    <row r="23" spans="1:12" ht="32" customHeight="1">
+      <c r="A23" s="5"/>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
@@ -1343,22 +1414,23 @@
         <v>18</v>
       </c>
       <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>31</v>
       </c>
+      <c r="F23" s="5"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="6" t="s">
+      <c r="H23" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J23" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
     </row>
-    <row r="24" spans="2:12" ht="32" customHeight="1">
+    <row r="24" spans="1:12" ht="32" customHeight="1">
+      <c r="A24" s="3"/>
       <c r="B24" s="1" t="s">
         <v>8</v>
       </c>
@@ -1366,22 +1438,23 @@
         <v>18</v>
       </c>
       <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J24" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J24" s="3"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
     </row>
-    <row r="25" spans="2:12" ht="32" customHeight="1">
+    <row r="25" spans="1:12" ht="32" customHeight="1">
+      <c r="A25" s="5"/>
       <c r="B25" s="6" t="s">
         <v>8</v>
       </c>
@@ -1389,22 +1462,23 @@
         <v>18</v>
       </c>
       <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>33</v>
       </c>
+      <c r="F25" s="5"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="6" t="s">
+      <c r="H25" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J25" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
     </row>
-    <row r="26" spans="2:12" ht="32" customHeight="1">
+    <row r="26" spans="1:12" ht="32" customHeight="1">
+      <c r="A26" s="3"/>
       <c r="B26" s="1" t="s">
         <v>10</v>
       </c>
@@ -1412,22 +1486,23 @@
         <v>18</v>
       </c>
       <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J26" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
     </row>
-    <row r="27" spans="2:12" ht="32" customHeight="1">
+    <row r="27" spans="1:12" ht="32" customHeight="1">
+      <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
         <v>8</v>
       </c>
@@ -1435,22 +1510,23 @@
         <v>18</v>
       </c>
       <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>35</v>
       </c>
+      <c r="F27" s="5"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="6" t="s">
+      <c r="H27" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J27" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J27" s="5"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
     </row>
-    <row r="28" spans="2:12" ht="32" customHeight="1">
+    <row r="28" spans="1:12" ht="32" customHeight="1">
+      <c r="A28" s="3"/>
       <c r="B28" s="1" t="s">
         <v>10</v>
       </c>
@@ -1458,22 +1534,23 @@
         <v>18</v>
       </c>
       <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="F28" s="3"/>
       <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J28" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J28" s="3"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
     </row>
-    <row r="29" spans="2:12" ht="32" customHeight="1">
+    <row r="29" spans="1:12" ht="32" customHeight="1">
+      <c r="A29" s="5"/>
       <c r="B29" s="6" t="s">
         <v>3</v>
       </c>
@@ -1481,22 +1558,23 @@
         <v>37</v>
       </c>
       <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>38</v>
       </c>
+      <c r="F29" s="5"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="6" t="s">
+      <c r="H29" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J29" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
     </row>
-    <row r="30" spans="2:12" ht="32" customHeight="1">
+    <row r="30" spans="1:12" ht="32" customHeight="1">
+      <c r="A30" s="3"/>
       <c r="B30" s="1" t="s">
         <v>3</v>
       </c>
@@ -1504,22 +1582,23 @@
         <v>39</v>
       </c>
       <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>40</v>
       </c>
+      <c r="F30" s="3"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J30" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J30" s="3"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
     </row>
-    <row r="31" spans="2:12" ht="32" customHeight="1">
+    <row r="31" spans="1:12" ht="32" customHeight="1">
+      <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
         <v>10</v>
       </c>
@@ -1527,22 +1606,23 @@
         <v>18</v>
       </c>
       <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>41</v>
       </c>
+      <c r="F31" s="5"/>
       <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="6" t="s">
+      <c r="H31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J31" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J31" s="5"/>
       <c r="K31" s="5"/>
       <c r="L31" s="5"/>
     </row>
-    <row r="32" spans="2:12" ht="32" customHeight="1">
+    <row r="32" spans="1:12" ht="32" customHeight="1">
+      <c r="A32" s="3"/>
       <c r="B32" s="1" t="s">
         <v>3</v>
       </c>
@@ -1550,22 +1630,23 @@
         <v>37</v>
       </c>
       <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>42</v>
       </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J32" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I32" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J32" s="3"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
     </row>
-    <row r="33" spans="2:12" ht="32" customHeight="1">
+    <row r="33" spans="1:12" ht="32" customHeight="1">
+      <c r="A33" s="5"/>
       <c r="B33" s="6" t="s">
         <v>3</v>
       </c>
@@ -1573,22 +1654,23 @@
         <v>39</v>
       </c>
       <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="5" t="s">
+      <c r="E33" s="5" t="s">
         <v>40</v>
       </c>
+      <c r="F33" s="5"/>
       <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="6" t="s">
+      <c r="H33" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J33" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
     </row>
-    <row r="34" spans="2:12" ht="32" customHeight="1">
+    <row r="34" spans="1:12" ht="32" customHeight="1">
+      <c r="A34" s="3"/>
       <c r="B34" s="1" t="s">
         <v>10</v>
       </c>
@@ -1596,22 +1678,23 @@
         <v>18</v>
       </c>
       <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="1" t="s">
+      <c r="H34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J34" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I34" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J34" s="3"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
     </row>
-    <row r="35" spans="2:12" ht="32" customHeight="1">
+    <row r="35" spans="1:12" ht="32" customHeight="1">
+      <c r="A35" s="5"/>
       <c r="B35" s="6" t="s">
         <v>3</v>
       </c>
@@ -1619,22 +1702,23 @@
         <v>37</v>
       </c>
       <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>43</v>
       </c>
+      <c r="F35" s="5"/>
       <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="6" t="s">
+      <c r="H35" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J35" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I35" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
     </row>
-    <row r="36" spans="2:12" ht="32" customHeight="1">
+    <row r="36" spans="1:12" ht="32" customHeight="1">
+      <c r="A36" s="3"/>
       <c r="B36" s="1" t="s">
         <v>3</v>
       </c>
@@ -1642,22 +1726,23 @@
         <v>39</v>
       </c>
       <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="1" t="s">
+      <c r="H36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J36" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I36" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J36" s="3"/>
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
     </row>
-    <row r="37" spans="2:12" ht="32" customHeight="1">
+    <row r="37" spans="1:12" ht="32" customHeight="1">
+      <c r="A37" s="5"/>
       <c r="B37" s="6" t="s">
         <v>8</v>
       </c>
@@ -1665,22 +1750,23 @@
         <v>39</v>
       </c>
       <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>45</v>
       </c>
+      <c r="F37" s="5"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="6" t="s">
+      <c r="H37" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J37" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
     </row>
-    <row r="38" spans="2:12" ht="32" customHeight="1">
+    <row r="38" spans="1:12" ht="32" customHeight="1">
+      <c r="A38" s="3"/>
       <c r="B38" s="1" t="s">
         <v>10</v>
       </c>
@@ -1688,22 +1774,23 @@
         <v>39</v>
       </c>
       <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J38" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J38" s="3"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
     </row>
-    <row r="39" spans="2:12" ht="32" customHeight="1">
+    <row r="39" spans="1:12" ht="32" customHeight="1">
+      <c r="A39" s="5"/>
       <c r="B39" s="6" t="s">
         <v>10</v>
       </c>
@@ -1711,22 +1798,23 @@
         <v>39</v>
       </c>
       <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="5" t="s">
+      <c r="E39" s="5" t="s">
         <v>47</v>
       </c>
+      <c r="F39" s="5"/>
       <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="6" t="s">
+      <c r="H39" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J39" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I39" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
     </row>
-    <row r="40" spans="2:12" ht="32" customHeight="1">
+    <row r="40" spans="1:12" ht="32" customHeight="1">
+      <c r="A40" s="3"/>
       <c r="B40" s="1" t="s">
         <v>10</v>
       </c>
@@ -1734,22 +1822,23 @@
         <v>18</v>
       </c>
       <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>48</v>
       </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J40" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I40" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J40" s="3"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
     </row>
-    <row r="41" spans="2:12" ht="32" customHeight="1">
+    <row r="41" spans="1:12" ht="32" customHeight="1">
+      <c r="A41" s="5"/>
       <c r="B41" s="6" t="s">
         <v>10</v>
       </c>
@@ -1757,22 +1846,23 @@
         <v>18</v>
       </c>
       <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="5" t="s">
+      <c r="E41" s="5" t="s">
         <v>49</v>
       </c>
+      <c r="F41" s="5"/>
       <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="6" t="s">
+      <c r="H41" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J41" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
     </row>
-    <row r="42" spans="2:12" ht="32" customHeight="1">
+    <row r="42" spans="1:12" ht="32" customHeight="1">
+      <c r="A42" s="3"/>
       <c r="B42" s="1" t="s">
         <v>10</v>
       </c>
@@ -1780,22 +1870,23 @@
         <v>18</v>
       </c>
       <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J42" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J42" s="3"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
     </row>
-    <row r="43" spans="2:12" ht="32" customHeight="1">
+    <row r="43" spans="1:12" ht="32" customHeight="1">
+      <c r="A43" s="5"/>
       <c r="B43" s="6" t="s">
         <v>3</v>
       </c>
@@ -1803,22 +1894,23 @@
         <v>51</v>
       </c>
       <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>52</v>
       </c>
+      <c r="F43" s="5"/>
       <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="6" t="s">
+      <c r="H43" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J43" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I43" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J43" s="5"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
     </row>
-    <row r="44" spans="2:12" ht="32" customHeight="1">
+    <row r="44" spans="1:12" ht="32" customHeight="1">
+      <c r="A44" s="3"/>
       <c r="B44" s="1" t="s">
         <v>10</v>
       </c>
@@ -1826,22 +1918,23 @@
         <v>51</v>
       </c>
       <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="3" t="s">
+      <c r="E44" s="3" t="s">
         <v>53</v>
       </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J44" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
     </row>
-    <row r="45" spans="2:12" ht="32" customHeight="1">
+    <row r="45" spans="1:12" ht="32" customHeight="1">
+      <c r="A45" s="5"/>
       <c r="B45" s="6" t="s">
         <v>3</v>
       </c>
@@ -1849,22 +1942,23 @@
         <v>51</v>
       </c>
       <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>54</v>
       </c>
+      <c r="F45" s="5"/>
       <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="6" t="s">
+      <c r="H45" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J45" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I45" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J45" s="5"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="46" spans="2:12" ht="32" customHeight="1">
+    <row r="46" spans="1:12" ht="32" customHeight="1">
+      <c r="A46" s="3"/>
       <c r="B46" s="1" t="s">
         <v>10</v>
       </c>
@@ -1872,22 +1966,23 @@
         <v>51</v>
       </c>
       <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>55</v>
       </c>
+      <c r="F46" s="3"/>
       <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J46" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
     </row>
-    <row r="47" spans="2:12" ht="32" customHeight="1">
+    <row r="47" spans="1:12" ht="32" customHeight="1">
+      <c r="A47" s="5"/>
       <c r="B47" s="6" t="s">
         <v>3</v>
       </c>
@@ -1895,22 +1990,23 @@
         <v>51</v>
       </c>
       <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="5" t="s">
+      <c r="E47" s="5" t="s">
         <v>56</v>
       </c>
+      <c r="F47" s="5"/>
       <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="6" t="s">
+      <c r="H47" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J47" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J47" s="5"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
     </row>
-    <row r="48" spans="2:12" ht="32" customHeight="1">
+    <row r="48" spans="1:12" ht="32" customHeight="1">
+      <c r="A48" s="3"/>
       <c r="B48" s="1" t="s">
         <v>10</v>
       </c>
@@ -1918,22 +2014,23 @@
         <v>51</v>
       </c>
       <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="3" t="s">
+      <c r="E48" s="3" t="s">
         <v>57</v>
       </c>
+      <c r="F48" s="3"/>
       <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J48" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J48" s="3"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
     </row>
-    <row r="49" spans="2:12" ht="32" customHeight="1">
+    <row r="49" spans="1:12" ht="32" customHeight="1">
+      <c r="A49" s="5"/>
       <c r="B49" s="6" t="s">
         <v>10</v>
       </c>
@@ -1941,22 +2038,23 @@
         <v>51</v>
       </c>
       <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="5" t="s">
+      <c r="E49" s="5" t="s">
         <v>58</v>
       </c>
+      <c r="F49" s="5"/>
       <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="6" t="s">
+      <c r="H49" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J49" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I49" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J49" s="5"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
     </row>
-    <row r="50" spans="2:12" ht="32" customHeight="1">
+    <row r="50" spans="1:12" ht="32" customHeight="1">
+      <c r="A50" s="3"/>
       <c r="B50" s="1" t="s">
         <v>10</v>
       </c>
@@ -1964,22 +2062,23 @@
         <v>51</v>
       </c>
       <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>59</v>
       </c>
+      <c r="F50" s="3"/>
       <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="1" t="s">
+      <c r="H50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J50" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J50" s="3"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
     </row>
-    <row r="51" spans="2:12" ht="32" customHeight="1">
+    <row r="51" spans="1:12" ht="32" customHeight="1">
+      <c r="A51" s="5"/>
       <c r="B51" s="6" t="s">
         <v>10</v>
       </c>
@@ -1987,22 +2086,23 @@
         <v>60</v>
       </c>
       <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="5" t="s">
+      <c r="E51" s="5" t="s">
         <v>61</v>
       </c>
+      <c r="F51" s="5"/>
       <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="6" t="s">
+      <c r="H51" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J51" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J51" s="5"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
     </row>
-    <row r="52" spans="2:12" ht="32" customHeight="1">
+    <row r="52" spans="1:12" ht="32" customHeight="1">
+      <c r="A52" s="3"/>
       <c r="B52" s="1" t="s">
         <v>8</v>
       </c>
@@ -2010,22 +2110,23 @@
         <v>60</v>
       </c>
       <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="3" t="s">
+      <c r="E52" s="3" t="s">
         <v>62</v>
       </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="1" t="s">
+      <c r="H52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J52" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J52" s="3"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
     </row>
-    <row r="53" spans="2:12" ht="32" customHeight="1">
+    <row r="53" spans="1:12" ht="32" customHeight="1">
+      <c r="A53" s="5"/>
       <c r="B53" s="6" t="s">
         <v>10</v>
       </c>
@@ -2033,22 +2134,23 @@
         <v>60</v>
       </c>
       <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="5" t="s">
+      <c r="E53" s="5" t="s">
         <v>63</v>
       </c>
+      <c r="F53" s="5"/>
       <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="6" t="s">
+      <c r="H53" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J53" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I53" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J53" s="5"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
     </row>
-    <row r="54" spans="2:12" ht="32" customHeight="1">
+    <row r="54" spans="1:12" ht="32" customHeight="1">
+      <c r="A54" s="3"/>
       <c r="B54" s="1" t="s">
         <v>10</v>
       </c>
@@ -2056,22 +2158,23 @@
         <v>60</v>
       </c>
       <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="3" t="s">
+      <c r="E54" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="F54" s="3"/>
       <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="1" t="s">
+      <c r="H54" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J54" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I54" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J54" s="3"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
     </row>
-    <row r="55" spans="2:12" ht="32" customHeight="1">
+    <row r="55" spans="1:12" ht="32" customHeight="1">
+      <c r="A55" s="5"/>
       <c r="B55" s="6" t="s">
         <v>10</v>
       </c>
@@ -2079,22 +2182,23 @@
         <v>60</v>
       </c>
       <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="5" t="s">
+      <c r="E55" s="5" t="s">
         <v>65</v>
       </c>
+      <c r="F55" s="5"/>
       <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="6" t="s">
+      <c r="H55" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J55" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
     </row>
-    <row r="56" spans="2:12" ht="32" customHeight="1">
+    <row r="56" spans="1:12" ht="32" customHeight="1">
+      <c r="A56" s="3"/>
       <c r="B56" s="1" t="s">
         <v>8</v>
       </c>
@@ -2102,22 +2206,23 @@
         <v>60</v>
       </c>
       <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="3" t="s">
+      <c r="E56" s="3" t="s">
         <v>66</v>
       </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="1" t="s">
+      <c r="H56" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J56" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J56" s="3"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
     </row>
-    <row r="57" spans="2:12" ht="32" customHeight="1">
+    <row r="57" spans="1:12" ht="32" customHeight="1">
+      <c r="A57" s="5"/>
       <c r="B57" s="6" t="s">
         <v>10</v>
       </c>
@@ -2125,22 +2230,23 @@
         <v>60</v>
       </c>
       <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="5" t="s">
+      <c r="E57" s="5" t="s">
         <v>67</v>
       </c>
+      <c r="F57" s="5"/>
       <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="6" t="s">
+      <c r="H57" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J57" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
     </row>
-    <row r="58" spans="2:12" ht="32" customHeight="1">
+    <row r="58" spans="1:12" ht="32" customHeight="1">
+      <c r="A58" s="3"/>
       <c r="B58" s="1" t="s">
         <v>8</v>
       </c>
@@ -2148,22 +2254,23 @@
         <v>60</v>
       </c>
       <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="3" t="s">
+      <c r="E58" s="3" t="s">
         <v>68</v>
       </c>
+      <c r="F58" s="3"/>
       <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="1" t="s">
+      <c r="H58" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J58" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J58" s="3"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
     </row>
-    <row r="59" spans="2:12" ht="32" customHeight="1">
+    <row r="59" spans="1:12" ht="32" customHeight="1">
+      <c r="A59" s="5"/>
       <c r="B59" s="6" t="s">
         <v>10</v>
       </c>
@@ -2171,22 +2278,23 @@
         <v>60</v>
       </c>
       <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="5" t="s">
+      <c r="E59" s="5" t="s">
         <v>69</v>
       </c>
+      <c r="F59" s="5"/>
       <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
-      <c r="I59" s="6" t="s">
+      <c r="H59" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J59" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J59" s="5"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
     </row>
-    <row r="60" spans="2:12" ht="32" customHeight="1">
+    <row r="60" spans="1:12" ht="32" customHeight="1">
+      <c r="A60" s="3"/>
       <c r="B60" s="1" t="s">
         <v>10</v>
       </c>
@@ -2194,22 +2302,23 @@
         <v>60</v>
       </c>
       <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="3" t="s">
+      <c r="E60" s="3" t="s">
         <v>70</v>
       </c>
+      <c r="F60" s="3"/>
       <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="1" t="s">
+      <c r="H60" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J60" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I60" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J60" s="3"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
     </row>
-    <row r="61" spans="2:12" ht="32" customHeight="1">
+    <row r="61" spans="1:12" ht="32" customHeight="1">
+      <c r="A61" s="5"/>
       <c r="B61" s="6" t="s">
         <v>10</v>
       </c>
@@ -2217,22 +2326,23 @@
         <v>60</v>
       </c>
       <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="5" t="s">
+      <c r="E61" s="5" t="s">
         <v>71</v>
       </c>
+      <c r="F61" s="5"/>
       <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="6" t="s">
+      <c r="H61" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J61" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J61" s="5"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
     </row>
-    <row r="62" spans="2:12" ht="32" customHeight="1">
+    <row r="62" spans="1:12" ht="32" customHeight="1">
+      <c r="A62" s="3"/>
       <c r="B62" s="1" t="s">
         <v>10</v>
       </c>
@@ -2240,22 +2350,23 @@
         <v>72</v>
       </c>
       <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="3" t="s">
+      <c r="E62" s="3" t="s">
         <v>73</v>
       </c>
+      <c r="F62" s="3"/>
       <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="1" t="s">
+      <c r="H62" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J62" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J62" s="3"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
     </row>
-    <row r="63" spans="2:12" ht="32" customHeight="1">
+    <row r="63" spans="1:12" ht="32" customHeight="1">
+      <c r="A63" s="5"/>
       <c r="B63" s="6" t="s">
         <v>10</v>
       </c>
@@ -2263,22 +2374,23 @@
         <v>72</v>
       </c>
       <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="5" t="s">
+      <c r="E63" s="5" t="s">
         <v>74</v>
       </c>
+      <c r="F63" s="5"/>
       <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="6" t="s">
+      <c r="H63" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J63" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J63" s="5"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
     </row>
-    <row r="64" spans="2:12" ht="32" customHeight="1">
+    <row r="64" spans="1:12" ht="32" customHeight="1">
+      <c r="A64" s="3"/>
       <c r="B64" s="1" t="s">
         <v>10</v>
       </c>
@@ -2286,22 +2398,23 @@
         <v>72</v>
       </c>
       <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="3" t="s">
+      <c r="E64" s="3" t="s">
         <v>75</v>
       </c>
+      <c r="F64" s="3"/>
       <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="1" t="s">
+      <c r="H64" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J64" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I64" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J64" s="3"/>
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
     </row>
-    <row r="65" spans="2:12" ht="32" customHeight="1">
+    <row r="65" spans="1:12" ht="32" customHeight="1">
+      <c r="A65" s="5"/>
       <c r="B65" s="6" t="s">
         <v>10</v>
       </c>
@@ -2309,22 +2422,23 @@
         <v>72</v>
       </c>
       <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="5" t="s">
+      <c r="E65" s="5" t="s">
         <v>76</v>
       </c>
+      <c r="F65" s="5"/>
       <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="6" t="s">
+      <c r="H65" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J65" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J65" s="5"/>
       <c r="K65" s="5"/>
       <c r="L65" s="5"/>
     </row>
-    <row r="66" spans="2:12" ht="32" customHeight="1">
+    <row r="66" spans="1:12" ht="32" customHeight="1">
+      <c r="A66" s="3"/>
       <c r="B66" s="1" t="s">
         <v>10</v>
       </c>
@@ -2332,22 +2446,23 @@
         <v>72</v>
       </c>
       <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="3" t="s">
+      <c r="E66" s="3" t="s">
         <v>77</v>
       </c>
+      <c r="F66" s="3"/>
       <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="1" t="s">
+      <c r="H66" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J66" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J66" s="3"/>
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
     </row>
-    <row r="67" spans="2:12" ht="32" customHeight="1">
+    <row r="67" spans="1:12" ht="32" customHeight="1">
+      <c r="A67" s="5"/>
       <c r="B67" s="6" t="s">
         <v>10</v>
       </c>
@@ -2355,22 +2470,23 @@
         <v>72</v>
       </c>
       <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="5" t="s">
+      <c r="E67" s="5" t="s">
         <v>78</v>
       </c>
+      <c r="F67" s="5"/>
       <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="6" t="s">
+      <c r="H67" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J67" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J67" s="5"/>
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
     </row>
-    <row r="68" spans="2:12" ht="32" customHeight="1">
+    <row r="68" spans="1:12" ht="32" customHeight="1">
+      <c r="A68" s="3"/>
       <c r="B68" s="1" t="s">
         <v>10</v>
       </c>
@@ -2378,22 +2494,23 @@
         <v>72</v>
       </c>
       <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>79</v>
       </c>
+      <c r="F68" s="3"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="1" t="s">
+      <c r="H68" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J68" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J68" s="3"/>
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
     </row>
-    <row r="69" spans="2:12" ht="32" customHeight="1">
+    <row r="69" spans="1:12" ht="32" customHeight="1">
+      <c r="A69" s="5"/>
       <c r="B69" s="6" t="s">
         <v>10</v>
       </c>
@@ -2401,22 +2518,23 @@
         <v>80</v>
       </c>
       <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="5" t="s">
+      <c r="E69" s="5" t="s">
         <v>81</v>
       </c>
+      <c r="F69" s="5"/>
       <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-      <c r="I69" s="6" t="s">
+      <c r="H69" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J69" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I69" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J69" s="5"/>
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
     </row>
-    <row r="70" spans="2:12" ht="32" customHeight="1">
+    <row r="70" spans="1:12" ht="32" customHeight="1">
+      <c r="A70" s="3"/>
       <c r="B70" s="1" t="s">
         <v>10</v>
       </c>
@@ -2424,22 +2542,23 @@
         <v>80</v>
       </c>
       <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>82</v>
       </c>
+      <c r="F70" s="3"/>
       <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="1" t="s">
+      <c r="H70" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J70" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I70" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J70" s="3"/>
       <c r="K70" s="5"/>
       <c r="L70" s="5"/>
     </row>
-    <row r="71" spans="2:12" ht="32" customHeight="1">
+    <row r="71" spans="1:12" ht="32" customHeight="1">
+      <c r="A71" s="5"/>
       <c r="B71" s="6" t="s">
         <v>10</v>
       </c>
@@ -2447,22 +2566,23 @@
         <v>80</v>
       </c>
       <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="5" t="s">
+      <c r="E71" s="5" t="s">
         <v>83</v>
       </c>
+      <c r="F71" s="5"/>
       <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="6" t="s">
+      <c r="H71" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J71" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J71" s="5"/>
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
     </row>
-    <row r="72" spans="2:12" ht="32" customHeight="1">
+    <row r="72" spans="1:12" ht="32" customHeight="1">
+      <c r="A72" s="3"/>
       <c r="B72" s="1" t="s">
         <v>10</v>
       </c>
@@ -2470,22 +2590,23 @@
         <v>80</v>
       </c>
       <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>84</v>
       </c>
+      <c r="F72" s="3"/>
       <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="1" t="s">
+      <c r="H72" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J72" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I72" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J72" s="3"/>
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
     </row>
-    <row r="73" spans="2:12" ht="32" customHeight="1">
+    <row r="73" spans="1:12" ht="32" customHeight="1">
+      <c r="A73" s="5"/>
       <c r="B73" s="6" t="s">
         <v>10</v>
       </c>
@@ -2493,22 +2614,23 @@
         <v>80</v>
       </c>
       <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="5" t="s">
+      <c r="E73" s="5" t="s">
         <v>85</v>
       </c>
+      <c r="F73" s="5"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
-      <c r="I73" s="6" t="s">
+      <c r="H73" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J73" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I73" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J73" s="5"/>
       <c r="K73" s="5"/>
       <c r="L73" s="5"/>
     </row>
-    <row r="74" spans="2:12" ht="32" customHeight="1">
+    <row r="74" spans="1:12" ht="32" customHeight="1">
+      <c r="A74" s="3"/>
       <c r="B74" s="1" t="s">
         <v>10</v>
       </c>
@@ -2516,22 +2638,23 @@
         <v>80</v>
       </c>
       <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>86</v>
       </c>
+      <c r="F74" s="3"/>
       <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="1" t="s">
+      <c r="H74" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J74" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I74" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J74" s="3"/>
       <c r="K74" s="5"/>
       <c r="L74" s="5"/>
     </row>
-    <row r="75" spans="2:12" ht="32" customHeight="1">
+    <row r="75" spans="1:12" ht="32" customHeight="1">
+      <c r="A75" s="5"/>
       <c r="B75" s="6" t="s">
         <v>10</v>
       </c>
@@ -2539,22 +2662,23 @@
         <v>80</v>
       </c>
       <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="5" t="s">
+      <c r="E75" s="5" t="s">
         <v>87</v>
       </c>
+      <c r="F75" s="5"/>
       <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-      <c r="I75" s="6" t="s">
+      <c r="H75" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J75" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I75" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J75" s="5"/>
       <c r="K75" s="5"/>
       <c r="L75" s="5"/>
     </row>
-    <row r="76" spans="2:12" ht="32" customHeight="1">
+    <row r="76" spans="1:12" ht="32" customHeight="1">
+      <c r="A76" s="3"/>
       <c r="B76" s="1" t="s">
         <v>10</v>
       </c>
@@ -2562,22 +2686,23 @@
         <v>80</v>
       </c>
       <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="3" t="s">
+      <c r="E76" s="3" t="s">
         <v>88</v>
       </c>
+      <c r="F76" s="3"/>
       <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="1" t="s">
+      <c r="H76" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J76" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J76" s="3"/>
       <c r="K76" s="5"/>
       <c r="L76" s="5"/>
     </row>
-    <row r="77" spans="2:12" ht="32" customHeight="1">
+    <row r="77" spans="1:12" ht="32" customHeight="1">
+      <c r="A77" s="5"/>
       <c r="B77" s="6" t="s">
         <v>10</v>
       </c>
@@ -2585,22 +2710,23 @@
         <v>80</v>
       </c>
       <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="5" t="s">
+      <c r="E77" s="5" t="s">
         <v>89</v>
       </c>
+      <c r="F77" s="5"/>
       <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
-      <c r="I77" s="6" t="s">
+      <c r="H77" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J77" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J77" s="5"/>
       <c r="K77" s="5"/>
       <c r="L77" s="5"/>
     </row>
-    <row r="78" spans="2:12" ht="32" customHeight="1">
+    <row r="78" spans="1:12" ht="32" customHeight="1">
+      <c r="A78" s="3"/>
       <c r="B78" s="1" t="s">
         <v>10</v>
       </c>
@@ -2608,22 +2734,23 @@
         <v>80</v>
       </c>
       <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="3" t="s">
+      <c r="E78" s="3" t="s">
         <v>90</v>
       </c>
+      <c r="F78" s="3"/>
       <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="1" t="s">
+      <c r="H78" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J78" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I78" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J78" s="3"/>
       <c r="K78" s="5"/>
       <c r="L78" s="5"/>
     </row>
-    <row r="79" spans="2:12" ht="32" customHeight="1">
+    <row r="79" spans="1:12" ht="32" customHeight="1">
+      <c r="A79" s="5"/>
       <c r="B79" s="6" t="s">
         <v>10</v>
       </c>
@@ -2631,22 +2758,23 @@
         <v>80</v>
       </c>
       <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="5" t="s">
+      <c r="E79" s="5" t="s">
         <v>91</v>
       </c>
+      <c r="F79" s="5"/>
       <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
-      <c r="I79" s="6" t="s">
+      <c r="H79" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J79" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I79" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J79" s="5"/>
       <c r="K79" s="5"/>
       <c r="L79" s="5"/>
     </row>
-    <row r="80" spans="2:12" ht="32" customHeight="1">
+    <row r="80" spans="1:12" ht="32" customHeight="1">
+      <c r="A80" s="3"/>
       <c r="B80" s="1" t="s">
         <v>10</v>
       </c>
@@ -2654,22 +2782,23 @@
         <v>80</v>
       </c>
       <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="3" t="s">
+      <c r="E80" s="3" t="s">
         <v>92</v>
       </c>
+      <c r="F80" s="3"/>
       <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="1" t="s">
+      <c r="H80" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J80" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I80" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J80" s="3"/>
       <c r="K80" s="5"/>
       <c r="L80" s="5"/>
     </row>
-    <row r="81" spans="2:12" ht="32" customHeight="1">
+    <row r="81" spans="1:12" ht="32" customHeight="1">
+      <c r="A81" s="5"/>
       <c r="B81" s="6" t="s">
         <v>10</v>
       </c>
@@ -2677,22 +2806,23 @@
         <v>80</v>
       </c>
       <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="5" t="s">
+      <c r="E81" s="5" t="s">
         <v>93</v>
       </c>
+      <c r="F81" s="5"/>
       <c r="G81" s="5"/>
-      <c r="H81" s="5"/>
-      <c r="I81" s="6" t="s">
+      <c r="H81" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J81" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I81" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J81" s="5"/>
       <c r="K81" s="5"/>
       <c r="L81" s="5"/>
     </row>
-    <row r="82" spans="2:12" ht="32" customHeight="1">
+    <row r="82" spans="1:12" ht="32" customHeight="1">
+      <c r="A82" s="3"/>
       <c r="B82" s="1" t="s">
         <v>10</v>
       </c>
@@ -2700,22 +2830,23 @@
         <v>80</v>
       </c>
       <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="3" t="s">
+      <c r="E82" s="3" t="s">
         <v>94</v>
       </c>
+      <c r="F82" s="3"/>
       <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="1" t="s">
+      <c r="H82" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J82" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J82" s="3"/>
       <c r="K82" s="5"/>
       <c r="L82" s="5"/>
     </row>
-    <row r="83" spans="2:12" ht="32" customHeight="1">
+    <row r="83" spans="1:12" ht="32" customHeight="1">
+      <c r="A83" s="5"/>
       <c r="B83" s="6" t="s">
         <v>8</v>
       </c>
@@ -2723,22 +2854,23 @@
         <v>95</v>
       </c>
       <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="5" t="s">
+      <c r="E83" s="5" t="s">
         <v>96</v>
       </c>
+      <c r="F83" s="5"/>
       <c r="G83" s="5"/>
-      <c r="H83" s="5"/>
-      <c r="I83" s="6" t="s">
+      <c r="H83" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J83" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I83" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J83" s="5"/>
       <c r="K83" s="5"/>
       <c r="L83" s="5"/>
     </row>
-    <row r="84" spans="2:12" ht="32" customHeight="1">
+    <row r="84" spans="1:12" ht="32" customHeight="1">
+      <c r="A84" s="3"/>
       <c r="B84" s="1" t="s">
         <v>8</v>
       </c>
@@ -2746,22 +2878,23 @@
         <v>95</v>
       </c>
       <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="3" t="s">
+      <c r="E84" s="3" t="s">
         <v>97</v>
       </c>
+      <c r="F84" s="3"/>
       <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="1" t="s">
+      <c r="H84" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J84" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I84" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J84" s="3"/>
       <c r="K84" s="5"/>
       <c r="L84" s="5"/>
     </row>
-    <row r="85" spans="2:12" ht="32" customHeight="1">
+    <row r="85" spans="1:12" ht="32" customHeight="1">
+      <c r="A85" s="5"/>
       <c r="B85" s="6" t="s">
         <v>8</v>
       </c>
@@ -2769,22 +2902,23 @@
         <v>95</v>
       </c>
       <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="5" t="s">
+      <c r="E85" s="5" t="s">
         <v>98</v>
       </c>
+      <c r="F85" s="5"/>
       <c r="G85" s="5"/>
-      <c r="H85" s="5"/>
-      <c r="I85" s="6" t="s">
+      <c r="H85" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J85" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I85" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J85" s="5"/>
       <c r="K85" s="5"/>
       <c r="L85" s="5"/>
     </row>
-    <row r="86" spans="2:12" ht="32" customHeight="1">
+    <row r="86" spans="1:12" ht="32" customHeight="1">
+      <c r="A86" s="3"/>
       <c r="B86" s="1" t="s">
         <v>8</v>
       </c>
@@ -2792,22 +2926,23 @@
         <v>95</v>
       </c>
       <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="3" t="s">
+      <c r="E86" s="3" t="s">
         <v>99</v>
       </c>
+      <c r="F86" s="3"/>
       <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="1" t="s">
+      <c r="H86" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J86" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I86" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J86" s="3"/>
       <c r="K86" s="5"/>
       <c r="L86" s="5"/>
     </row>
-    <row r="87" spans="2:12" ht="32" customHeight="1">
+    <row r="87" spans="1:12" ht="32" customHeight="1">
+      <c r="A87" s="5"/>
       <c r="B87" s="6" t="s">
         <v>8</v>
       </c>
@@ -2815,22 +2950,23 @@
         <v>95</v>
       </c>
       <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="5" t="s">
+      <c r="E87" s="5" t="s">
         <v>100</v>
       </c>
+      <c r="F87" s="5"/>
       <c r="G87" s="5"/>
-      <c r="H87" s="5"/>
-      <c r="I87" s="6" t="s">
+      <c r="H87" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J87" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J87" s="5"/>
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
     </row>
-    <row r="88" spans="2:12" ht="32" customHeight="1">
+    <row r="88" spans="1:12" ht="32" customHeight="1">
+      <c r="A88" s="3"/>
       <c r="B88" s="1" t="s">
         <v>10</v>
       </c>
@@ -2838,22 +2974,23 @@
         <v>51</v>
       </c>
       <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="3" t="s">
+      <c r="E88" s="3" t="s">
         <v>101</v>
       </c>
+      <c r="F88" s="3"/>
       <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="1" t="s">
+      <c r="H88" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J88" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I88" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J88" s="3"/>
       <c r="K88" s="5"/>
       <c r="L88" s="5"/>
     </row>
-    <row r="89" spans="2:12" ht="32" customHeight="1">
+    <row r="89" spans="1:12" ht="32" customHeight="1">
+      <c r="A89" s="5"/>
       <c r="B89" s="6" t="s">
         <v>10</v>
       </c>
@@ -2861,22 +2998,23 @@
         <v>51</v>
       </c>
       <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="5" t="s">
+      <c r="E89" s="5" t="s">
         <v>102</v>
       </c>
+      <c r="F89" s="5"/>
       <c r="G89" s="5"/>
-      <c r="H89" s="5"/>
-      <c r="I89" s="6" t="s">
+      <c r="H89" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J89" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I89" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J89" s="5"/>
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
     </row>
-    <row r="90" spans="2:12" ht="32" customHeight="1">
+    <row r="90" spans="1:12" ht="32" customHeight="1">
+      <c r="A90" s="3"/>
       <c r="B90" s="1" t="s">
         <v>3</v>
       </c>
@@ -2884,22 +3022,22 @@
         <v>4</v>
       </c>
       <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="3" t="s">
+      <c r="E90" s="3" t="s">
         <v>103</v>
       </c>
+      <c r="F90" s="3"/>
       <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="1" t="s">
+      <c r="H90" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J90" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I90" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J90" s="3"/>
       <c r="K90" s="5"/>
       <c r="L90" s="5"/>
     </row>
-    <row r="91" spans="2:12" ht="14">
+    <row r="91" spans="1:12" ht="14">
       <c r="B91" s="6"/>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
@@ -2911,7 +3049,7 @@
       <c r="J91" s="4"/>
       <c r="K91" s="5"/>
     </row>
-    <row r="92" spans="2:12" ht="14">
+    <row r="92" spans="1:12" ht="14">
       <c r="B92" s="1"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
@@ -2923,7 +3061,7 @@
       <c r="J92" s="4"/>
       <c r="K92" s="5"/>
     </row>
-    <row r="93" spans="2:12" ht="14">
+    <row r="93" spans="1:12" ht="14">
       <c r="B93" s="6"/>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
@@ -2935,7 +3073,7 @@
       <c r="J93" s="4"/>
       <c r="K93" s="5"/>
     </row>
-    <row r="94" spans="2:12" ht="14">
+    <row r="94" spans="1:12" ht="14">
       <c r="B94" s="1"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
@@ -2947,7 +3085,7 @@
       <c r="J94" s="4"/>
       <c r="K94" s="5"/>
     </row>
-    <row r="95" spans="2:12" ht="14">
+    <row r="95" spans="1:12" ht="14">
       <c r="B95" s="6"/>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
@@ -2959,7 +3097,7 @@
       <c r="J95" s="4"/>
       <c r="K95" s="5"/>
     </row>
-    <row r="96" spans="2:12" ht="14">
+    <row r="96" spans="1:12" ht="14">
       <c r="B96" s="1"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
@@ -7078,21 +7216,38 @@
       <c r="I1048" s="8"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J248">
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Funciona">
-      <formula>NOT(ISERROR(SEARCH("Funciona",J2)))</formula>
+  <conditionalFormatting sqref="J91:J248">
+    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="Funciona">
+      <formula>NOT(ISERROR(SEARCH("Funciona",J91)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Falla">
-      <formula>NOT(ISERROR(SEARCH("Falla",J2)))</formula>
+    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="Falla">
+      <formula>NOT(ISERROR(SEARCH("Falla",J91)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH("N/A",J2)))</formula>
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="N/A">
+      <formula>NOT(ISERROR(SEARCH("N/A",J91)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="Pendiente">
-      <formula>NOT(ISERROR(SEARCH("Pendiente",J2)))</formula>
+    <cfRule type="containsText" dxfId="6" priority="10" operator="containsText" text="Pendiente">
+      <formula>NOT(ISERROR(SEARCH("Pendiente",J91)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="Por ejecutar">
-      <formula>NOT(ISERROR(SEARCH("Por ejecutar",J2)))</formula>
+    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="Por ejecutar">
+      <formula>NOT(ISERROR(SEARCH("Por ejecutar",J91)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I90">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Funciona">
+      <formula>NOT(ISERROR(SEARCH("Funciona",I2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Falla">
+      <formula>NOT(ISERROR(SEARCH("Falla",I2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="N/A">
+      <formula>NOT(ISERROR(SEARCH("N/A",I2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Pendiente">
+      <formula>NOT(ISERROR(SEARCH("Pendiente",I2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Por ejecutar">
+      <formula>NOT(ISERROR(SEARCH("Por ejecutar",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -7100,7 +7255,7 @@
       <formula1>"Acceso,Buscador,Control Compras,Control Parental,Navegación,NPVR,Perfiles,Rep. Canal Líneal,Reproducción,TimeShift,Transacción,Claro Música,Trickplay,Social y Settings"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J234 J236" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I90 J236 J91:J234" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Funciona,Falla nueva,Falla persiste,N/A,Pendiente,Por ejecutar,"</formula1>
       <formula2>0</formula2>
     </dataValidation>
